--- a/Nifty_Bias_Console.xlsx
+++ b/Nifty_Bias_Console.xlsx
@@ -343,9 +343,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Console'!$A$10:$A$13</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -362,8 +362,9 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
@@ -375,6 +376,7 @@
           <max val="100"/>
           <min val="-100"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -392,7 +394,7 @@
             </rich>
           </tx>
         </title>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
